--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -3080,19 +3080,23 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Baggbölesmyran, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620887</v>
+        <v>620909</v>
       </c>
       <c r="R25" t="n">
-        <v>6897890</v>
+        <v>6897880</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3130,6 +3134,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136596642</v>
       </c>
       <c r="B6" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136596641</v>
       </c>
       <c r="B7" t="n">
-        <v>92295</v>
+        <v>92298</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136596626</v>
       </c>
       <c r="B8" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136596633</v>
       </c>
       <c r="B9" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136596629</v>
       </c>
       <c r="B10" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>136596647</v>
       </c>
       <c r="B26" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136596642</v>
       </c>
       <c r="B6" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136596641</v>
       </c>
       <c r="B7" t="n">
-        <v>92298</v>
+        <v>92299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136596626</v>
       </c>
       <c r="B8" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136596633</v>
       </c>
       <c r="B9" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136596629</v>
       </c>
       <c r="B10" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>136596647</v>
       </c>
       <c r="B26" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136596617</v>
       </c>
       <c r="B2" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136596620</v>
       </c>
       <c r="B3" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136596623</v>
       </c>
       <c r="B4" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136596645</v>
       </c>
       <c r="B5" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136596642</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136596641</v>
       </c>
       <c r="B7" t="n">
-        <v>92299</v>
+        <v>92304</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136596626</v>
       </c>
       <c r="B8" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136596633</v>
       </c>
       <c r="B9" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136596629</v>
       </c>
       <c r="B10" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136596618</v>
       </c>
       <c r="B11" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136596619</v>
       </c>
       <c r="B12" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136596621</v>
       </c>
       <c r="B13" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136596638</v>
       </c>
       <c r="B14" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136596639</v>
       </c>
       <c r="B15" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136596644</v>
       </c>
       <c r="B16" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136596622</v>
       </c>
       <c r="B17" t="n">
-        <v>75564</v>
+        <v>75566</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136596631</v>
       </c>
       <c r="B18" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136596628</v>
       </c>
       <c r="B19" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136596624</v>
       </c>
       <c r="B20" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136596625</v>
       </c>
       <c r="B21" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136596632</v>
       </c>
       <c r="B22" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>136596635</v>
       </c>
       <c r="B23" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620909</v>
+        <v>620917</v>
       </c>
       <c r="R25" t="n">
-        <v>6897880</v>
+        <v>6897874</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3161,7 +3161,7 @@
         <v>136596647</v>
       </c>
       <c r="B26" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136596642</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136596641</v>
       </c>
       <c r="B7" t="n">
-        <v>92304</v>
+        <v>92306</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136596626</v>
       </c>
       <c r="B8" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136596633</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136596629</v>
       </c>
       <c r="B10" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>136596647</v>
       </c>
       <c r="B26" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136596617</v>
       </c>
       <c r="B2" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136596620</v>
       </c>
       <c r="B3" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136596623</v>
       </c>
       <c r="B4" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136596645</v>
       </c>
       <c r="B5" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136596642</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136596641</v>
       </c>
       <c r="B7" t="n">
-        <v>92306</v>
+        <v>92308</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136596626</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136596633</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136596629</v>
       </c>
       <c r="B10" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136596618</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136596619</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136596621</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136596638</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136596639</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136596644</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136596631</v>
       </c>
       <c r="B18" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136596628</v>
       </c>
       <c r="B19" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>136596647</v>
       </c>
       <c r="B26" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136596617</v>
       </c>
       <c r="B2" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136596620</v>
       </c>
       <c r="B3" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136596623</v>
       </c>
       <c r="B4" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136596645</v>
       </c>
       <c r="B5" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136596642</v>
       </c>
       <c r="B6" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136596641</v>
       </c>
       <c r="B7" t="n">
-        <v>92308</v>
+        <v>92310</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136596626</v>
       </c>
       <c r="B8" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136596633</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136596629</v>
       </c>
       <c r="B10" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136596618</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136596619</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136596621</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136596638</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136596639</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136596644</v>
       </c>
       <c r="B16" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136596631</v>
       </c>
       <c r="B18" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136596628</v>
       </c>
       <c r="B19" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>136596647</v>
       </c>
       <c r="B26" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136596617</v>
       </c>
       <c r="B2" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136596620</v>
       </c>
       <c r="B3" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136596623</v>
       </c>
       <c r="B4" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136596645</v>
       </c>
       <c r="B5" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136596642</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136596641</v>
       </c>
       <c r="B7" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136596626</v>
       </c>
       <c r="B8" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136596633</v>
       </c>
       <c r="B9" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136596629</v>
       </c>
       <c r="B10" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136596618</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136596619</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136596621</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136596638</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136596639</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136596644</v>
       </c>
       <c r="B16" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136596631</v>
       </c>
       <c r="B18" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136596628</v>
       </c>
       <c r="B19" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>136596647</v>
       </c>
       <c r="B26" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>136596642</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136596641</v>
       </c>
       <c r="B7" t="n">
-        <v>92311</v>
+        <v>92317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136596626</v>
       </c>
       <c r="B8" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136596633</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136596629</v>
       </c>
       <c r="B10" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>136596647</v>
       </c>
       <c r="B26" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136596617</v>
       </c>
       <c r="B2" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136596620</v>
       </c>
       <c r="B3" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136596623</v>
       </c>
       <c r="B4" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136596645</v>
       </c>
       <c r="B5" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136596642</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136596641</v>
       </c>
       <c r="B7" t="n">
-        <v>92317</v>
+        <v>92321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136596626</v>
       </c>
       <c r="B8" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136596633</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136596629</v>
       </c>
       <c r="B10" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136596618</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136596619</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136596621</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136596638</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136596639</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136596644</v>
       </c>
       <c r="B16" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136596631</v>
       </c>
       <c r="B18" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136596628</v>
       </c>
       <c r="B19" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>136596647</v>
       </c>
       <c r="B26" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>136596647</v>
       </c>
       <c r="B26" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136596617</v>
       </c>
       <c r="B2" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136596620</v>
       </c>
       <c r="B3" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136596623</v>
       </c>
       <c r="B4" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136596645</v>
       </c>
       <c r="B5" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136596642</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136596641</v>
       </c>
       <c r="B7" t="n">
-        <v>92321</v>
+        <v>92323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136596626</v>
       </c>
       <c r="B8" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136596633</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136596629</v>
       </c>
       <c r="B10" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136596618</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136596619</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136596621</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136596638</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136596639</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136596644</v>
       </c>
       <c r="B16" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136596631</v>
       </c>
       <c r="B18" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136596628</v>
       </c>
       <c r="B19" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>136596647</v>
       </c>
       <c r="B26" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136596617</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136596620</v>
       </c>
       <c r="B3" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136596623</v>
       </c>
       <c r="B4" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136596645</v>
       </c>
       <c r="B5" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136596642</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136596641</v>
       </c>
       <c r="B7" t="n">
-        <v>92323</v>
+        <v>92336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136596626</v>
       </c>
       <c r="B8" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136596633</v>
       </c>
       <c r="B9" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136596629</v>
       </c>
       <c r="B10" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136596618</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136596619</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136596621</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136596638</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136596639</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136596644</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136596622</v>
       </c>
       <c r="B17" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136596631</v>
       </c>
       <c r="B18" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136596628</v>
       </c>
       <c r="B19" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136596624</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136596625</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>136596632</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>136596635</v>
       </c>
       <c r="B23" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>136596647</v>
       </c>
       <c r="B26" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 35606-2026 artfynd.xlsx
+++ b/artfynd/A 35606-2026 artfynd.xlsx
@@ -3054,7 +3054,7 @@
         <v>136596627</v>
       </c>
       <c r="B25" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
